--- a/submission/knowledge/A07-武汉商户助手/武汉商户助手QA导入表.xlsx
+++ b/submission/knowledge/A07-武汉商户助手/武汉商户助手QA导入表.xlsx
@@ -877,6 +877,193 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥要网上约吗？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">个人一般不用。团体讲解要约。南北区闭馆日不同。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">辛亥</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川阁公众号？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「武汉晴川阁大禹文化博物馆」。电话027-84710887。夜游另一套。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晴川</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我抢武大樱花？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不能。走学校官方预约。没有名额改东湖。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖樱园多少钱？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以「游东湖」当天为准，不背死数字。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱园</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博电话？</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">027-86716789，时段以馆方为准。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">电话</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">归元寺春节怎么买？</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">看市政府通告和「武汉归元禅寺」公众号，近年春节线上购票、夜间不开放。</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">归元</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜上黄鹤楼在哪个公众号买？</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">「夜上黄鹤楼」。不要用日场票混夜场。</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两江游船官方在哪买？</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">官方售票平台或码头窗口。不是通勤轮渡。</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">游船入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖游船用哪个小程序？</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优先「游东湖」。电话027-86793760咨询。</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">东湖程序</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">有没有东湖全含联票？</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">以官方当年产品为准，不保证。</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">联票</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场没票？</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改江滩看照明。不找黄牛。</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">没票</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>